--- a/Icons/таблица 106хам.xlsx
+++ b/Icons/таблица 106хам.xlsx
@@ -4,6 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <sheets>
     <sheet name="Лист1" r:id="rId1" sheetId="1" state="visible"/>
+    <sheet name="Лист2" r:id="rId2" sheetId="2" state="visible"/>
   </sheets>
   <definedNames/>
   <calcPr calcCompleted="true" calcMode="auto" calcOnSave="false" fullCalcOnLoad="false"/>
@@ -30,7 +31,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -38,12 +39,84 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </left>
+      <right style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </right>
+      <top style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </left>
+      <top style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </right>
+      <top style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </left>
+      <right style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </left>
+      <right style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </right>
+      <top style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </left>
+      <right style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="0C0C0C" tint="0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="1" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="2" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="3" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="4" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="5" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="6" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle builtinId="0" name="Normal" xfId="0"/>
@@ -272,8 +345,420 @@
       <c r="A1" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="B1" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="2">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A2, 3)</f>
+        <v>001</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A2=0, "", IF(MOD(A2, 2)=1, 1, IF(MOD(A2, 4)=2, 2, IF(MOD(A2, 8)=4, 3, IF(MOD(A2, 16)=8, 4, 5)))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A3, 3)</f>
+        <v>010</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A3=0, "", IF(MOD(A3, 2)=1, 1, IF(MOD(A3, 4)=2, 2, IF(MOD(A3, 8)=4, 3, IF(MOD(A3, 16)=8, 4, 5)))))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A4, 3)</f>
+        <v>011</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A4=0, "", IF(MOD(A4, 2)=1, 1, IF(MOD(A4, 4)=2, 2, IF(MOD(A4, 8)=4, 3, IF(MOD(A4, 16)=8, 4, 5)))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A5, 3)</f>
+        <v>100</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A5=0, "", IF(MOD(A5, 2)=1, 1, IF(MOD(A5, 4)=2, 2, IF(MOD(A5, 8)=4, 3, IF(MOD(A5, 16)=8, 4, 5)))))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="6">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A6, 3)</f>
+        <v>101</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A6=0, "", IF(MOD(A6, 2)=1, 1, IF(MOD(A6, 4)=2, 2, IF(MOD(A6, 8)=4, 3, IF(MOD(A6, 16)=8, 4, 5)))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="7">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A7, 3)</f>
+        <v>110</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A7=0, "", IF(MOD(A7, 2)=1, 1, IF(MOD(A7, 4)=2, 2, IF(MOD(A7, 8)=4, 3, IF(MOD(A7, 16)=8, 4, 5)))))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="8">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A8, 3)</f>
+        <v>111</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A8=0, "", IF(MOD(A8, 2)=1, 1, IF(MOD(A8, 4)=2, 2, IF(MOD(A8, 8)=4, 3, IF(MOD(A8, 16)=8, 4, 5)))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="9">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="str">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">DEC2BIN(A9, 3)</f>
+        <v>1000</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">IF(A9=0, "", IF(MOD(A9, 2)=1, 1, IF(MOD(A9, 4)=2, 2, IF(MOD(A9, 8)=4, 3, IF(MOD(A9, 16)=8, 4, 5)))))</f>
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.59055554866790771" footer="0.19680555164813995" header="0.19680555164813995" left="0.59055554866790771" right="0.59055554866790771" top="0.59055554866790771"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:Z300"/>
+  <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="10.788470377394527" defaultRowHeight="15" zeroHeight="false"/>
+  <cols>
+    <col customWidth="true" max="8" min="1" outlineLevel="0" width="10.056398989942563"/>
+  </cols>
+  <sheetData>
+    <row outlineLevel="0" r="1">
+      <c r="A1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="2">
+      <c r="A2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5">
+      <c r="A5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="6">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="7">
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="8">
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="9">
+      <c r="A9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="10">
+      <c r="A10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="11">
+      <c r="A11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="12">
+      <c r="A12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="13">
+      <c r="A13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.59055554866790771" footer="0.5" header="0.5" left="0.59055554866790771" right="0.59055554866790771" top="0.59055554866790771"/>
+  <pageSetup fitToHeight="0" fitToWidth="0" orientation="portrait" paperHeight="297.1798mm" paperSize="9" paperWidth="210.0438mm" scale="100"/>
+</worksheet>
 </file>